--- a/results/Int Task Remove ACC -0.5/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_10_permute.xlsx
@@ -440,177 +440,177 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6842766403501672</v>
+        <v>0.6874283821628049</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6839844135821952</v>
+        <v>0.6846706080767468</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6974403979928069</v>
+        <v>0.6904269555614801</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6977071895211269</v>
+        <v>0.658751170578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6980497297923519</v>
+        <v>0.677073269085527</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.687262217640991</v>
+        <v>0.677073269085527</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6856105979917672</v>
+        <v>0.6816217211748185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6872243432695386</v>
+        <v>0.6837176220538752</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7005655906136911</v>
+        <v>0.6843529460691229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6993333739306988</v>
+        <v>0.707451856846758</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7262074683804696</v>
+        <v>0.706078910881604</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7346322881244537</v>
+        <v>0.6934611754274049</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7319768119730542</v>
+        <v>0.6660783761845952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7212830574569068</v>
+        <v>0.6557605805027191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7224265292891426</v>
+        <v>0.6522414201552552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7496431640101384</v>
+        <v>0.6382767309516048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.763175454139706</v>
+        <v>0.6354437650986924</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7550937316429976</v>
+        <v>0.6360282186346363</v>
       </c>
     </row>
     <row r="20">
@@ -620,57 +620,57 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7281082419830724</v>
+        <v>0.6303617299527611</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7298361673512521</v>
+        <v>0.6168543180867947</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7238390205539016</v>
+        <v>0.6168543180867947</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.717078259590942</v>
+        <v>0.6177174453068084</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.717078259590942</v>
+        <v>0.6369552124418053</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7240272784590627</v>
+        <v>0.6271839959244205</v>
       </c>
     </row>
     <row r="26">
@@ -680,647 +680,647 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7133014049906539</v>
+        <v>0.6267645929581889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7069476078621254</v>
+        <v>0.6400068842239875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7159455559623544</v>
+        <v>0.6527009253971425</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7224666315647982</v>
+        <v>0.6520656013818947</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7111071050092941</v>
+        <v>0.6520656013818947</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6716395963928745</v>
+        <v>0.6856507002674228</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6534728942035131</v>
+        <v>0.7237474908228914</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6760783242001638</v>
+        <v>0.7163903941682379</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6504483285891351</v>
+        <v>0.7360622313054701</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6582745847372224</v>
+        <v>0.696391797747886</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6658600415726925</v>
+        <v>0.7040795525180145</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6539160614812445</v>
+        <v>0.706849765735873</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7092984181137524</v>
+        <v>0.6754717772808726</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7282439584807773</v>
+        <v>0.6751541152732488</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7364810772956512</v>
+        <v>0.5856202151115771</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7361888505276791</v>
+        <v>0.6430097277723854</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7361888505276791</v>
+        <v>0.6162785905089796</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7433679005047689</v>
+        <v>0.635031974138488</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6835960156161232</v>
+        <v>0.6349811036591841</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6709149705508196</v>
+        <v>0.6243213246821337</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6691616099429879</v>
+        <v>0.6113361706931084</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.621072483377978</v>
+        <v>0.6278280458977972</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5725316492357917</v>
+        <v>0.6210813949947904</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5733071455571506</v>
+        <v>0.6157580035601909</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5733071455571506</v>
+        <v>0.6149321937355789</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5832422986921459</v>
+        <v>0.5805766113131491</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5608182572293635</v>
+        <v>0.5751006084406378</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5855682306801717</v>
+        <v>0.5546322955508011</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5884661770723408</v>
+        <v>0.5355488107818681</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6541273410631707</v>
+        <v>0.5416465845857249</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.649807249154696</v>
+        <v>0.5452420506521447</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6486762164542608</v>
+        <v>0.5518604114047901</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6511530889520458</v>
+        <v>0.5531056241956338</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6511530889520458</v>
+        <v>0.5431433648928341</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6556009140348311</v>
+        <v>0.5413136985660466</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6556009140348311</v>
+        <v>0.5349186852097609</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6689924748822367</v>
+        <v>0.5463810666759744</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6850068359527298</v>
+        <v>0.5509430718491679</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6850057220006283</v>
+        <v>0.6204031838236331</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.656221199696708</v>
+        <v>0.6196152483704738</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6591779998915753</v>
+        <v>0.6080132515742001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6594956618991992</v>
+        <v>0.5102099279867098</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7018588890035846</v>
+        <v>0.5236675833254738</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7046664196168451</v>
+        <v>0.532117281333059</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7100287993749986</v>
+        <v>0.5401470193983618</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7097365726070266</v>
+        <v>0.524428412610829</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.742368685469683</v>
+        <v>0.524428412610829</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7300816081309591</v>
+        <v>0.5217883461301676</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7300816081309591</v>
+        <v>0.5211740015461654</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7162604330897244</v>
+        <v>0.5161298407716866</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.667187872477734</v>
+        <v>0.5161298407716866</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6636291668306651</v>
+        <v>0.510629516611625</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6354001353080485</v>
+        <v>0.511188534907917</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6388429899365567</v>
+        <v>0.4584284215224458</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6366962185781961</v>
+        <v>0.4581616299941258</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6361372002819041</v>
+        <v>0.4721597377608227</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6547775177731058</v>
+        <v>0.478398797822892</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6704576932131354</v>
+        <v>0.4790341218381398</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6801656001194156</v>
+        <v>0.49045807195685</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6126493345621462</v>
+        <v>0.4974460791485247</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5733071455571506</v>
+        <v>0.5035822842998848</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5727226920212066</v>
+        <v>0.4910900541157931</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5665458276181402</v>
+        <v>0.4701739324811352</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5022869436644717</v>
+        <v>0.5086574500745233</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5005714574280925</v>
+        <v>0.4968909596845882</v>
       </c>
     </row>
   </sheetData>
